--- a/education_surveys/033_endline_survey_for_character_policy--education_surveys.xlsx
+++ b/education_surveys/033_endline_survey_for_character_policy--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Improvement Ideas Awareness</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Effectiveness</t>
+          <t>Improvement Ideas Effectiveness</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Challenges</t>
+          <t>Improvement Ideas Challenges</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Awareness Level</t>
+          <t>Improvement Ideas Awareness Level</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Character Policy Awareness</t>
+          <t>Improvement Ideas Character Policy Awareness</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Character Policy Effectiveness</t>
+          <t>Improvement Ideas Character Policy Effectiveness</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>awareness_level</t>
+          <t>awareness_level_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Awareness Level</t>
+          <t>Awareness Level 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>character_policy_awareness</t>
+          <t>character_policy_awareness_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Character Policy Awareness</t>
+          <t>Character Policy Awareness 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>character_policy_effectiveness</t>
+          <t>character_policy_effectiveness_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Character Policy Effectiveness</t>
+          <t>Character Policy Effectiveness 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>school_character</t>
+          <t>school_character_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>School Character</t>
+          <t>School Character 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>awareness_level_choices</t>
+          <t>awareness_level_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>awareness_level_choices</t>
+          <t>awareness_level_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>character_policy_awareness_choices</t>
+          <t>character_policy_awareness_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>character_policy_awareness_choices</t>
+          <t>character_policy_awareness_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>character_policy_effectiveness_choices</t>
+          <t>character_policy_effectiveness_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>character_policy_effectiveness_choices</t>
+          <t>character_policy_effectiveness_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>school_character_choices</t>
+          <t>school_character_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>school_character_choices</t>
+          <t>school_character_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
